--- a/data/lsd/mic/2026-03-25 09.56.21 Run.xlsx
+++ b/data/lsd/mic/2026-03-25 09.56.21 Run.xlsx
@@ -72,7 +72,7 @@
     <t>File Exported</t>
   </si>
   <si>
-    <t>30/03/2026 12:09:16</t>
+    <t>16/04/2026 14:42:28</t>
   </si>
   <si>
     <t>Software Version</t>
